--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="57" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="95" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="95" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="114" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="114" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="171" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="171" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="228" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="228" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="285" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="285" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="399" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="399" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="418" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="418" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="57" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="114" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="133" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="133" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="171" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="171" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="361" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="361" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="380" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="380" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="399" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="418" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="475" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="475" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="513" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="513" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="532" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="532" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="570" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="570" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="589" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="589" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="608" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="608" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="646" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="646" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="665" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="665" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="722" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="722" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="779" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="779" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="798" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="798" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="855" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="855" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="874" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="874" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="893" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="893" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="950" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="950" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="969" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="969" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="950" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="969" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1026" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1026" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1045" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1045" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1064" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1064" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1102" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1102" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1159" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>

--- a/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
+++ b/outputs/master_rename_build/tables/fold_multi_weighing_approach.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1159" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1197" uniqueCount="14">
   <si>
     <t>pull_province</t>
   </si>
